--- a/artfynd/A 23491-2026 artfynd.xlsx
+++ b/artfynd/A 23491-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,6 +892,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134268237</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488633</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6666411</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23491-2026 artfynd.xlsx
+++ b/artfynd/A 23491-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134197238</v>
       </c>
       <c r="B2" t="n">
-        <v>99082</v>
+        <v>99084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>134197900</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23491-2026 artfynd.xlsx
+++ b/artfynd/A 23491-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134197238</v>
       </c>
       <c r="B2" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>134197900</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23491-2026 artfynd.xlsx
+++ b/artfynd/A 23491-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134197238</v>
+        <v>134197900</v>
       </c>
       <c r="B2" t="n">
-        <v>99092</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 50 st blommande ex</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,48 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134197900</v>
+        <v>134268237</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gettjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488656</v>
+        <v>488633</v>
       </c>
       <c r="R3" t="n">
-        <v>6666392</v>
+        <v>6666411</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,14 +884,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134268237</v>
+        <v>134268364</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -925,7 +915,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488633</v>
+        <v>488674</v>
       </c>
       <c r="R4" t="n">
-        <v>6666411</v>
+        <v>6666508</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,6 +983,342 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134194391</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>488685</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6666403</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134195368</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488664</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666468</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Betade tqllar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134197238</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gettjärnsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488656</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666392</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 50 st blommande ex</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
